--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.93817</v>
+        <v>16.47213</v>
       </c>
       <c r="D2" t="n">
-        <v>16.38182</v>
+        <v>16.63773</v>
       </c>
       <c r="E2" t="n">
-        <v>16.85299</v>
+        <v>16.53411</v>
       </c>
       <c r="F2" t="n">
-        <v>43.48457</v>
+        <v>43.41474</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05016</v>
+        <v>0.05067</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80622</v>
+        <v>1.8113</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.84814</v>
+        <v>16.75804</v>
       </c>
       <c r="D3" t="n">
-        <v>16.61247</v>
+        <v>16.12524</v>
       </c>
       <c r="E3" t="n">
-        <v>16.68779</v>
+        <v>16.47327</v>
       </c>
       <c r="F3" t="n">
-        <v>41.71767</v>
+        <v>4245.157</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05132</v>
+        <v>0.05115</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8299</v>
+        <v>1.83808</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.43579</v>
+        <v>16.58034</v>
       </c>
       <c r="D4" t="n">
-        <v>16.42144</v>
+        <v>16.45385</v>
       </c>
       <c r="E4" t="n">
-        <v>16.66166</v>
+        <v>16.45921</v>
       </c>
       <c r="F4" t="n">
-        <v>42.23501</v>
+        <v>43.08163</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04976</v>
+        <v>0.05071</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82009</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.55901</v>
+        <v>16.53548</v>
       </c>
       <c r="D5" t="n">
-        <v>16.57687</v>
+        <v>16.31454</v>
       </c>
       <c r="E5" t="n">
-        <v>16.54449</v>
+        <v>16.40681</v>
       </c>
       <c r="F5" t="n">
-        <v>42.17864</v>
+        <v>42.33973</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04994</v>
+        <v>0.0504</v>
       </c>
       <c r="H5" t="n">
-        <v>1.87089</v>
+        <v>1.84261</v>
       </c>
     </row>
     <row r="6">
@@ -559,10 +559,23 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>scratched - not measurable</t>
-        </is>
+      <c r="C6" t="n">
+        <v>16.87048</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.46852</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16.51308</v>
+      </c>
+      <c r="F6" t="n">
+        <v>41.53689</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.05111</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.7728</v>
       </c>
     </row>
     <row r="7">
@@ -572,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.8016</v>
+        <v>16.43298</v>
       </c>
       <c r="D7" t="n">
-        <v>16.74053</v>
+        <v>16.32488</v>
       </c>
       <c r="E7" t="n">
-        <v>16.5501</v>
+        <v>16.41548</v>
       </c>
       <c r="F7" t="n">
-        <v>41.75295</v>
+        <v>41.5576</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04953</v>
+        <v>0.04986</v>
       </c>
       <c r="H7" t="n">
-        <v>1.79898</v>
+        <v>1.81142</v>
       </c>
     </row>
     <row r="8">
@@ -597,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.82027</v>
+        <v>16.58918</v>
       </c>
       <c r="D8" t="n">
-        <v>16.58548</v>
+        <v>16.21868</v>
       </c>
       <c r="E8" t="n">
-        <v>16.17012</v>
+        <v>16.51952</v>
       </c>
       <c r="F8" t="n">
-        <v>41.73451</v>
+        <v>41.71285</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05089</v>
+        <v>0.05049</v>
       </c>
       <c r="H8" t="n">
-        <v>1.84489</v>
+        <v>1.79009</v>
       </c>
     </row>
     <row r="9">
@@ -622,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.86457</v>
+        <v>16.63923</v>
       </c>
       <c r="D9" t="n">
-        <v>16.54241</v>
+        <v>16.5091</v>
       </c>
       <c r="E9" t="n">
-        <v>16.2628</v>
+        <v>16.51473</v>
       </c>
       <c r="F9" t="n">
-        <v>41.90819</v>
+        <v>42.30978</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05099</v>
+        <v>0.05022</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81481</v>
+        <v>1.79409</v>
       </c>
     </row>
     <row r="10">
@@ -647,48 +660,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.77796</v>
+        <v>16.83115</v>
       </c>
       <c r="D10" t="n">
-        <v>16.52861</v>
+        <v>16.54166</v>
       </c>
       <c r="E10" t="n">
-        <v>16.70587</v>
+        <v>16.62285</v>
       </c>
       <c r="F10" t="n">
-        <v>42.04266</v>
+        <v>43.11636</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05158</v>
+        <v>0.04974</v>
       </c>
       <c r="H10" t="n">
-        <v>1.80116</v>
+        <v>1.81723</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Space</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -700,23 +698,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.29012</v>
+        <v>0.61298</v>
       </c>
       <c r="D12" t="n">
-        <v>15.71173</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.52368</v>
-      </c>
-      <c r="F12" t="n">
-        <v>21.71573</v>
-      </c>
-      <c r="G12" t="n">
-        <v>34.4282</v>
+        <v>1.11954</v>
       </c>
     </row>
     <row r="13">
@@ -726,19 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.44186</v>
+        <v>0.61282</v>
       </c>
       <c r="D13" t="n">
-        <v>15.80427</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.07368</v>
-      </c>
-      <c r="F13" t="n">
-        <v>21.07622</v>
-      </c>
-      <c r="G13" t="n">
-        <v>33.98168</v>
+        <v>1.10427</v>
       </c>
     </row>
     <row r="14">
@@ -747,25 +727,11 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>re-measured</t>
-        </is>
-      </c>
       <c r="C14" t="n">
-        <v>16.78246</v>
+        <v>0.60304</v>
       </c>
       <c r="D14" t="n">
-        <v>15.55548</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.26679</v>
-      </c>
-      <c r="F14" t="n">
-        <v>21.5652</v>
-      </c>
-      <c r="G14" t="n">
-        <v>34.27846</v>
+        <v>1.09818</v>
       </c>
     </row>
     <row r="15">
@@ -775,19 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.63198</v>
+        <v>0.6128400000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>15.79368</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.10808</v>
-      </c>
-      <c r="F15" t="n">
-        <v>21.38351</v>
-      </c>
-      <c r="G15" t="n">
-        <v>33.75557</v>
+        <v>1.09476</v>
       </c>
     </row>
     <row r="16">
@@ -797,19 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.62977</v>
+        <v>0.59135</v>
       </c>
       <c r="D16" t="n">
-        <v>16.24659</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.12298</v>
-      </c>
-      <c r="F16" t="n">
-        <v>21.41181</v>
-      </c>
-      <c r="G16" t="n">
-        <v>33.17211</v>
+        <v>1.08643</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.77615</v>
+        <v>0.60449</v>
       </c>
       <c r="D17" t="n">
-        <v>15.93469</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.10218</v>
-      </c>
-      <c r="F17" t="n">
-        <v>21.25736</v>
-      </c>
-      <c r="G17" t="n">
-        <v>33.81904</v>
+        <v>1.10291</v>
       </c>
     </row>
     <row r="18">
@@ -841,19 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.71274</v>
+        <v>0.61593</v>
       </c>
       <c r="D18" t="n">
-        <v>15.97954</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16.14531</v>
-      </c>
-      <c r="F18" t="n">
-        <v>22.0174</v>
-      </c>
-      <c r="G18" t="n">
-        <v>34.03565</v>
+        <v>1.08244</v>
       </c>
     </row>
     <row r="19">
@@ -863,19 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.76887</v>
+        <v>0.59378</v>
       </c>
       <c r="D19" t="n">
-        <v>15.72799</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.32657</v>
-      </c>
-      <c r="F19" t="n">
-        <v>21.78501</v>
-      </c>
-      <c r="G19" t="n">
-        <v>33.97202</v>
+        <v>1.10767</v>
       </c>
     </row>
     <row r="20">
@@ -885,19 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.27769</v>
+        <v>0.60783</v>
       </c>
       <c r="D20" t="n">
-        <v>15.7754</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.28198</v>
-      </c>
-      <c r="F20" t="n">
-        <v>21.65155</v>
-      </c>
-      <c r="G20" t="n">
-        <v>34.4094</v>
+        <v>1.0825</v>
       </c>
     </row>
     <row r="21">
@@ -954,28 +866,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.74028</v>
+        <v>0.73961</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08176</v>
+        <v>0.07949000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.61009</v>
+        <v>0.61536</v>
       </c>
       <c r="F22" t="n">
-        <v>0.95834</v>
+        <v>0.9781300000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>0.10848</v>
+        <v>0.10719</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00743</v>
+        <v>0.0075</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09304999999999999</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>0.12765</v>
+        <v>0.12373</v>
       </c>
     </row>
     <row r="23">
@@ -985,28 +897,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.75505</v>
+        <v>0.7382300000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08066</v>
+        <v>0.08006000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.58836</v>
+        <v>0.59368</v>
       </c>
       <c r="F23" t="n">
-        <v>0.94806</v>
+        <v>0.96344</v>
       </c>
       <c r="G23" t="n">
-        <v>0.10711</v>
+        <v>0.10949</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00747</v>
+        <v>0.00741</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09285</v>
+        <v>0.09155000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>0.12656</v>
+        <v>0.12453</v>
       </c>
     </row>
     <row r="24">
@@ -1016,28 +928,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.75088</v>
+        <v>0.74393</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08057</v>
+        <v>0.07954</v>
       </c>
       <c r="E24" t="n">
-        <v>0.59936</v>
+        <v>0.60234</v>
       </c>
       <c r="F24" t="n">
-        <v>0.94758</v>
+        <v>0.93575</v>
       </c>
       <c r="G24" t="n">
-        <v>0.10751</v>
+        <v>0.10754</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00746</v>
+        <v>0.00757</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09490999999999999</v>
+        <v>0.09186999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.12698</v>
+        <v>0.12506</v>
       </c>
     </row>
     <row r="25">
@@ -1047,28 +959,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7569</v>
+        <v>0.76157</v>
       </c>
       <c r="D25" t="n">
-        <v>0.07925</v>
+        <v>0.08071</v>
       </c>
       <c r="E25" t="n">
-        <v>0.59446</v>
+        <v>0.61529</v>
       </c>
       <c r="F25" t="n">
-        <v>0.94903</v>
+        <v>0.96245</v>
       </c>
       <c r="G25" t="n">
-        <v>0.10907</v>
+        <v>0.10991</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00751</v>
+        <v>0.00755</v>
       </c>
       <c r="I25" t="n">
-        <v>0.08992</v>
+        <v>0.09097</v>
       </c>
       <c r="J25" t="n">
-        <v>0.12597</v>
+        <v>0.12615</v>
       </c>
     </row>
     <row r="26">
@@ -1078,28 +990,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.74752</v>
+        <v>0.75298</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08108</v>
+        <v>0.08085000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6085700000000001</v>
+        <v>0.60032</v>
       </c>
       <c r="F26" t="n">
-        <v>0.96165</v>
+        <v>0.93904</v>
       </c>
       <c r="G26" t="n">
-        <v>0.10652</v>
+        <v>0.10944</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00749</v>
+        <v>0.00757</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09341000000000001</v>
+        <v>0.09224</v>
       </c>
       <c r="J26" t="n">
-        <v>0.12555</v>
+        <v>0.12601</v>
       </c>
     </row>
     <row r="27">
@@ -1109,28 +1021,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.74368</v>
+        <v>0.75044</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08105999999999999</v>
+        <v>0.08026999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6112300000000001</v>
+        <v>0.60598</v>
       </c>
       <c r="F27" t="n">
-        <v>0.95342</v>
+        <v>0.9424</v>
       </c>
       <c r="G27" t="n">
-        <v>0.10883</v>
+        <v>0.11128</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00754</v>
+        <v>0.00763</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09050999999999999</v>
+        <v>0.09168</v>
       </c>
       <c r="J27" t="n">
-        <v>0.12557</v>
+        <v>0.12541</v>
       </c>
     </row>
     <row r="28">
@@ -1140,28 +1052,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.74214</v>
+        <v>0.72929</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08041</v>
+        <v>0.08143</v>
       </c>
       <c r="E28" t="n">
-        <v>0.60325</v>
+        <v>0.59096</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9475</v>
+        <v>0.95048</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1063</v>
+        <v>0.10921</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00763</v>
+        <v>0.00788</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09211999999999999</v>
+        <v>0.09167</v>
       </c>
       <c r="J28" t="n">
-        <v>0.12697</v>
+        <v>0.12703</v>
       </c>
     </row>
     <row r="29">
@@ -1171,28 +1083,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.72194</v>
+        <v>0.75658</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08018</v>
+        <v>0.07874</v>
       </c>
       <c r="E29" t="n">
-        <v>0.61224</v>
+        <v>0.60349</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9660300000000001</v>
+        <v>0.93487</v>
       </c>
       <c r="G29" t="n">
-        <v>0.11093</v>
+        <v>0.1097</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0076</v>
+        <v>0.00754</v>
       </c>
       <c r="I29" t="n">
-        <v>0.092</v>
+        <v>0.09191000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>0.12436</v>
+        <v>0.12625</v>
       </c>
     </row>
     <row r="30">
@@ -1202,28 +1114,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.74722</v>
+        <v>0.75674</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08054</v>
+        <v>0.07983999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.60259</v>
+        <v>0.58723</v>
       </c>
       <c r="F30" t="n">
-        <v>0.95072</v>
+        <v>0.95736</v>
       </c>
       <c r="G30" t="n">
-        <v>0.10823</v>
+        <v>0.10907</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00746</v>
+        <v>0.0078</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09271</v>
+        <v>0.09254</v>
       </c>
       <c r="J30" t="n">
-        <v>0.12846</v>
+        <v>0.12392</v>
       </c>
     </row>
   </sheetData>
